--- a/danhsachisbn copy.xlsx
+++ b/danhsachisbn copy.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7596E69B-04C9-8A41-B7DD-40BA4C2E310B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14700" yWindow="660" windowWidth="14700" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -477,6 +477,106 @@
     <cellStyle name="Normal 7" xfId="1" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="94">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1317,106 +1417,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -10774,287 +10774,287 @@
       <c r="D2058" s="8"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="duplicateValues" dxfId="93" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="92" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="duplicateValues" dxfId="91" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4">
+    <cfRule type="duplicateValues" dxfId="90" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5">
+    <cfRule type="duplicateValues" dxfId="89" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6">
+    <cfRule type="duplicateValues" dxfId="88" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7">
+    <cfRule type="duplicateValues" dxfId="87" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8">
+    <cfRule type="duplicateValues" dxfId="86" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9">
+    <cfRule type="duplicateValues" dxfId="85" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10">
+    <cfRule type="duplicateValues" dxfId="84" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="duplicateValues" dxfId="83" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12">
+    <cfRule type="duplicateValues" dxfId="82" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="81" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="80" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15">
+    <cfRule type="duplicateValues" dxfId="79" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16">
+    <cfRule type="duplicateValues" dxfId="78" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" dxfId="77" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18">
+    <cfRule type="duplicateValues" dxfId="76" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19">
+    <cfRule type="duplicateValues" dxfId="75" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20">
+    <cfRule type="duplicateValues" dxfId="74" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21">
+    <cfRule type="duplicateValues" dxfId="73" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="72" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23">
+    <cfRule type="duplicateValues" dxfId="71" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24">
+    <cfRule type="duplicateValues" dxfId="70" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A25">
+    <cfRule type="duplicateValues" dxfId="69" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="68" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27">
+    <cfRule type="duplicateValues" dxfId="67" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A28">
+    <cfRule type="duplicateValues" dxfId="66" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29">
+    <cfRule type="duplicateValues" dxfId="65" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="64" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31">
+    <cfRule type="duplicateValues" dxfId="63" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A32">
+    <cfRule type="duplicateValues" dxfId="62" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A33">
+    <cfRule type="duplicateValues" dxfId="61" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A34">
+    <cfRule type="duplicateValues" dxfId="60" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35">
+    <cfRule type="duplicateValues" dxfId="59" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A36">
+    <cfRule type="duplicateValues" dxfId="58" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A37">
+    <cfRule type="duplicateValues" dxfId="57" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A38">
+    <cfRule type="duplicateValues" dxfId="56" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39">
+    <cfRule type="duplicateValues" dxfId="55" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A40">
+    <cfRule type="duplicateValues" dxfId="54" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A41">
+    <cfRule type="duplicateValues" dxfId="53" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A42">
+    <cfRule type="duplicateValues" dxfId="52" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" dxfId="51" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" dxfId="50" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A45">
+    <cfRule type="duplicateValues" dxfId="49" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46">
+    <cfRule type="duplicateValues" dxfId="48" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A47">
+    <cfRule type="duplicateValues" dxfId="47" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48">
+    <cfRule type="duplicateValues" dxfId="46" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A49">
+    <cfRule type="duplicateValues" dxfId="45" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A50">
+    <cfRule type="duplicateValues" dxfId="44" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51">
+    <cfRule type="duplicateValues" dxfId="43" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A52">
+    <cfRule type="duplicateValues" dxfId="42" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53">
+    <cfRule type="duplicateValues" dxfId="41" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" dxfId="40" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" dxfId="39" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" dxfId="38" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" dxfId="37" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58">
+    <cfRule type="duplicateValues" dxfId="36" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" dxfId="35" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" dxfId="34" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A61">
+    <cfRule type="duplicateValues" dxfId="33" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62">
+    <cfRule type="duplicateValues" dxfId="32" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A63">
+    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A64">
+    <cfRule type="duplicateValues" dxfId="30" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A65">
+    <cfRule type="duplicateValues" dxfId="29" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" dxfId="28" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A67">
+    <cfRule type="duplicateValues" dxfId="27" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A68">
+    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A70">
+    <cfRule type="duplicateValues" dxfId="24" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A71">
+    <cfRule type="duplicateValues" dxfId="23" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A72">
+    <cfRule type="duplicateValues" dxfId="22" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A73">
+    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A74">
+    <cfRule type="duplicateValues" dxfId="20" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A75">
+    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A76">
+    <cfRule type="duplicateValues" dxfId="18" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A77">
+    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A78">
+    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A79">
+    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A81">
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A82">
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A83">
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A84">
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A2059:A1048576">
-    <cfRule type="duplicateValues" dxfId="93" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E119">
-    <cfRule type="duplicateValues" dxfId="92" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E127">
-    <cfRule type="duplicateValues" dxfId="91" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E135">
-    <cfRule type="duplicateValues" dxfId="90" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E140">
-    <cfRule type="duplicateValues" dxfId="89" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E145">
-    <cfRule type="duplicateValues" dxfId="88" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E149">
-    <cfRule type="duplicateValues" dxfId="87" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E153">
-    <cfRule type="duplicateValues" dxfId="86" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G112">
-    <cfRule type="duplicateValues" dxfId="85" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G189">
-    <cfRule type="duplicateValues" dxfId="84" priority="86"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="83" priority="84"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="82" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3">
-    <cfRule type="duplicateValues" dxfId="81" priority="82"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="80" priority="81"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5">
-    <cfRule type="duplicateValues" dxfId="79" priority="80"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A6">
-    <cfRule type="duplicateValues" dxfId="78" priority="79"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7">
-    <cfRule type="duplicateValues" dxfId="77" priority="78"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="76" priority="77"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="75" priority="76"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A10">
-    <cfRule type="duplicateValues" dxfId="74" priority="75"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="73" priority="74"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="72" priority="73"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="71" priority="72"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="70" priority="71"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15">
-    <cfRule type="duplicateValues" dxfId="69" priority="70"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A16">
-    <cfRule type="duplicateValues" dxfId="68" priority="69"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="67" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18">
-    <cfRule type="duplicateValues" dxfId="66" priority="67"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19">
-    <cfRule type="duplicateValues" dxfId="65" priority="66"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A20">
-    <cfRule type="duplicateValues" dxfId="64" priority="65"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A21">
-    <cfRule type="duplicateValues" dxfId="63" priority="64"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="62" priority="63"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="61" priority="62"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A24">
-    <cfRule type="duplicateValues" dxfId="60" priority="61"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="59" priority="60"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="58" priority="59"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27">
-    <cfRule type="duplicateValues" dxfId="57" priority="58"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A28">
-    <cfRule type="duplicateValues" dxfId="56" priority="57"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A29">
-    <cfRule type="duplicateValues" dxfId="55" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
-    <cfRule type="duplicateValues" dxfId="54" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31">
-    <cfRule type="duplicateValues" dxfId="53" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A32">
-    <cfRule type="duplicateValues" dxfId="52" priority="53"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A33">
-    <cfRule type="duplicateValues" dxfId="51" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A34">
-    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35">
-    <cfRule type="duplicateValues" dxfId="49" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A36">
-    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A37">
-    <cfRule type="duplicateValues" dxfId="47" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A38">
-    <cfRule type="duplicateValues" dxfId="46" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39">
-    <cfRule type="duplicateValues" dxfId="45" priority="46"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A40">
-    <cfRule type="duplicateValues" dxfId="44" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A41">
-    <cfRule type="duplicateValues" dxfId="43" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A42">
-    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A43">
-    <cfRule type="duplicateValues" dxfId="41" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A44">
-    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A45">
-    <cfRule type="duplicateValues" dxfId="39" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A46">
-    <cfRule type="duplicateValues" dxfId="38" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A47">
-    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A48">
-    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A49">
-    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A50">
-    <cfRule type="duplicateValues" dxfId="34" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A52">
-    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A53">
-    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58">
-    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A59">
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A60">
-    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A61">
-    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A63">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A64">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A65">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A66">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A67">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A68">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A69">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A70">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A71">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A72">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A73">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A74">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A75">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A76">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A77">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A78">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A79">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A80">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A81">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A82">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A83">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A84">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
   </conditionalFormatting>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
